--- a/data/training_tweets.xlsx
+++ b/data/training_tweets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ubarcelona-my.sharepoint.com/personal/cvillavi156_alumnes_ub_edu/Documents/Documents/Analisis de contenido/content_analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="14_{29B5C1A4-1964-B84C-9FEA-8D40734FFDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F95B1578-F0FC-F441-A01B-B883CC7F9CA4}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="14_{29B5C1A4-1964-B84C-9FEA-8D40734FFDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{486886D1-411F-0E4F-B8EC-10D107316365}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17160" xr2:uid="{F85E1CCB-1FD7-7B43-A077-26131B5E9FFE}"/>
   </bookViews>
@@ -1238,12 +1238,6 @@
     <t>Disponible ya! Solamente en Guadalajara ❤️💯🙈😈👑🔥🤤 hermosa transexual dotada!🍆 22 cm! No te quedes con la duda &amp;amp; compruébalo. Dale #retweet y no olviden darle seguir a mi perfil para ver mi delicioso contenido. Tal cual en persona, así de hermosa 🔥🔥😍 url</t>
   </si>
   <si>
-    <t>@edriu_ocanto ¿Cuál misterio?
-La orientación sexual nada tiene que ver con el rol sexual.
-Que un hombre bisexual guste de ser penetrado, no lo hace menos bisexual, no hace que deje de sentirse atraído por mujeres.
-También hay que recordar que hay mujeres trans activas.</t>
-  </si>
-  <si>
     <t>Lo que viene siendo mi último #ofni de #FILGurl
 #HappyMoodOn #Fun #Queer #BeYourself #BeProud #GayBoy #InstaGay #InstaLinisho en Expo Guadalajara url</t>
   </si>
@@ -2029,6 +2023,12 @@
   </si>
   <si>
     <t xml:space="preserve"> @set7pablo @YaajMexico @Robotania @OphCourse @arty_kings @Aleejandralg @apoyo_trans @Alexan2613 @TVNAPzac @gj_lambdazac @Chuvajetik @ElMarshmallow @salvadorag105 @joveneslgbtmex Laura jamás ha atacado a personas trans, cuestiona que es muy distinto. Ophelia si ataca a mujeres como a la tatuadora que sufrió violencia por su parte.</t>
+  </si>
+  <si>
+    <t>¿Cuál misterio?
+La orientación sexual nada tiene que ver con el rol sexual.
+Que un hombre bisexual guste de ser penetrado, no lo hace menos bisexual, no hace que deje de sentirse atraído por mujeres.
+También hay que recordar que hay mujeres trans activas.</t>
   </si>
 </sst>
 </file>
@@ -2064,10 +2064,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2084,6 +2087,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3703,7 +3710,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -5254,7 +5261,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -8181,7 +8188,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -8869,7 +8876,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -8955,7 +8962,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -9987,7 +9994,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -13857,7 +13864,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -14631,7 +14638,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -18377,7 +18384,7 @@
         <v>0</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R186">
         <v>0</v>
@@ -19667,7 +19674,7 @@
         <v>0</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R201">
         <v>0</v>
@@ -19703,12 +19710,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:28" ht="68" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>201</v>
       </c>
-      <c r="B202" t="s">
-        <v>345</v>
+      <c r="B202" s="2" t="s">
+        <v>525</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -19794,7 +19801,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -19880,7 +19887,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -20138,7 +20145,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -20310,7 +20317,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -20482,7 +20489,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -20740,7 +20747,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -20826,7 +20833,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -20912,7 +20919,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -20998,7 +21005,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -21170,7 +21177,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -21256,7 +21263,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -21686,7 +21693,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -21772,7 +21779,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -21944,7 +21951,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -22374,7 +22381,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -22460,7 +22467,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -22718,7 +22725,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -22890,7 +22897,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -22976,7 +22983,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -23062,7 +23069,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -23320,7 +23327,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -23492,7 +23499,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -23578,7 +23585,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -24008,7 +24015,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -24094,7 +24101,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -24266,7 +24273,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -24438,7 +24445,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -24524,7 +24531,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -24696,7 +24703,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -24782,7 +24789,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -24868,7 +24875,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -24954,7 +24961,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -25126,7 +25133,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -25298,7 +25305,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -25556,7 +25563,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -25728,7 +25735,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -26072,7 +26079,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C276">
         <v>0</v>
@@ -26158,7 +26165,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -26244,7 +26251,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -26502,7 +26509,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -26588,7 +26595,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -26674,7 +26681,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -26760,7 +26767,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C284">
         <v>0</v>
@@ -26846,7 +26853,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -27018,7 +27025,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -27104,7 +27111,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -27190,7 +27197,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -27448,7 +27455,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -27620,7 +27627,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -27706,7 +27713,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -27792,7 +27799,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C296">
         <v>0</v>
@@ -27878,7 +27885,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -27964,7 +27971,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -28050,7 +28057,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -28308,7 +28315,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -28394,7 +28401,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -28480,7 +28487,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -28566,7 +28573,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -28652,7 +28659,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -28824,7 +28831,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -28910,7 +28917,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -28996,7 +29003,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -29082,7 +29089,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -29168,7 +29175,7 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -29254,7 +29261,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -29340,7 +29347,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -29856,7 +29863,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -29942,7 +29949,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -30200,7 +30207,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -30372,7 +30379,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -30458,7 +30465,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -30630,7 +30637,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -30716,7 +30723,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -30802,7 +30809,7 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C331">
         <v>0</v>
@@ -30888,7 +30895,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -31060,7 +31067,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -31232,7 +31239,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -31318,7 +31325,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C337">
         <v>0</v>
@@ -31834,7 +31841,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -32092,7 +32099,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C346">
         <v>0</v>
@@ -32178,7 +32185,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -32350,7 +32357,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C349">
         <v>0</v>
@@ -32436,7 +32443,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C350">
         <v>0</v>
@@ -32522,7 +32529,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C351">
         <v>0</v>
@@ -32608,7 +32615,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -32694,7 +32701,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -32780,7 +32787,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -32866,7 +32873,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -32952,7 +32959,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -33210,7 +33217,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C359">
         <v>0</v>
@@ -33468,7 +33475,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -33554,7 +33561,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C363">
         <v>0</v>
@@ -33898,7 +33905,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C367">
         <v>0</v>
@@ -34070,7 +34077,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C369">
         <v>0</v>
@@ -34414,7 +34421,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C373">
         <v>0</v>
@@ -34500,7 +34507,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -34586,7 +34593,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -34672,7 +34679,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C376">
         <v>0</v>
@@ -34844,7 +34851,7 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C378">
         <v>0</v>
@@ -35016,7 +35023,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C380">
         <v>0</v>
@@ -35102,7 +35109,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C381">
         <v>0</v>
@@ -35188,7 +35195,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C382">
         <v>0</v>
@@ -35274,7 +35281,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C383">
         <v>0</v>
@@ -35618,7 +35625,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -35704,7 +35711,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -35876,7 +35883,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C390">
         <v>0</v>
@@ -36134,7 +36141,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C393">
         <v>0</v>
@@ -36220,7 +36227,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C394">
         <v>0</v>
@@ -36822,7 +36829,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C401">
         <v>0</v>
@@ -36994,7 +37001,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C403">
         <v>0</v>
@@ -37080,7 +37087,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C404">
         <v>0</v>
@@ -37166,7 +37173,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C405">
         <v>0</v>
@@ -37252,7 +37259,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C406">
         <v>0</v>
@@ -37338,7 +37345,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C407">
         <v>0</v>
@@ -37424,7 +37431,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C408">
         <v>0</v>
@@ -37596,7 +37603,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C410">
         <v>0</v>
@@ -37682,7 +37689,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C411">
         <v>0</v>
@@ -37768,7 +37775,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C412">
         <v>0</v>
@@ -37940,7 +37947,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C414">
         <v>0</v>
@@ -38198,7 +38205,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C417">
         <v>0</v>
@@ -38284,7 +38291,7 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C418">
         <v>0</v>
@@ -38456,7 +38463,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C420">
         <v>0</v>
@@ -38542,7 +38549,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C421">
         <v>0</v>
@@ -38628,7 +38635,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C422">
         <v>0</v>
@@ -38886,7 +38893,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C425">
         <v>0</v>
@@ -38972,7 +38979,7 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C426">
         <v>0</v>
@@ -39144,7 +39151,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C428">
         <v>0</v>
@@ -39402,7 +39409,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C431">
         <v>0</v>
@@ -39574,7 +39581,7 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C433">
         <v>0</v>
@@ -39660,7 +39667,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C434">
         <v>0</v>
@@ -40004,7 +40011,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C438">
         <v>0</v>
@@ -40176,7 +40183,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C440">
         <v>0</v>
@@ -40434,7 +40441,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C443">
         <v>0</v>
@@ -40606,7 +40613,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C445">
         <v>0</v>
@@ -40692,7 +40699,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C446">
         <v>0</v>
@@ -40778,7 +40785,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C447">
         <v>0</v>
@@ -40864,7 +40871,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C448">
         <v>0</v>
@@ -40950,7 +40957,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C449">
         <v>0</v>
@@ -41036,7 +41043,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C450">
         <v>0</v>
@@ -41208,7 +41215,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C452">
         <v>0</v>
@@ -41294,7 +41301,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C453">
         <v>0</v>
@@ -41552,7 +41559,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C456">
         <v>0</v>
@@ -41810,7 +41817,7 @@
         <v>458</v>
       </c>
       <c r="B459" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C459">
         <v>0</v>
@@ -41896,7 +41903,7 @@
         <v>459</v>
       </c>
       <c r="B460" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C460">
         <v>0</v>
@@ -41982,7 +41989,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C461">
         <v>0</v>
@@ -42068,7 +42075,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C462">
         <v>0</v>
@@ -42240,7 +42247,7 @@
         <v>463</v>
       </c>
       <c r="B464" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C464">
         <v>0</v>
@@ -42326,7 +42333,7 @@
         <v>464</v>
       </c>
       <c r="B465" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C465">
         <v>0</v>
@@ -42412,7 +42419,7 @@
         <v>465</v>
       </c>
       <c r="B466" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C466">
         <v>0</v>
@@ -42670,7 +42677,7 @@
         <v>468</v>
       </c>
       <c r="B469" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C469">
         <v>0</v>
@@ -42756,7 +42763,7 @@
         <v>469</v>
       </c>
       <c r="B470" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C470">
         <v>0</v>
@@ -42842,7 +42849,7 @@
         <v>470</v>
       </c>
       <c r="B471" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C471">
         <v>0</v>
@@ -42928,7 +42935,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C472">
         <v>0</v>
@@ -43014,7 +43021,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C473">
         <v>0</v>
@@ -43186,7 +43193,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C475">
         <v>0</v>
@@ -43358,7 +43365,7 @@
         <v>476</v>
       </c>
       <c r="B477" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C477">
         <v>0</v>
@@ -43530,7 +43537,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C479">
         <v>0</v>
@@ -43702,7 +43709,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C481">
         <v>0</v>
@@ -43788,7 +43795,7 @@
         <v>481</v>
       </c>
       <c r="B482" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C482">
         <v>0</v>
@@ -43874,7 +43881,7 @@
         <v>482</v>
       </c>
       <c r="B483" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C483">
         <v>0</v>
@@ -44046,7 +44053,7 @@
         <v>484</v>
       </c>
       <c r="B485" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C485">
         <v>0</v>
@@ -44218,7 +44225,7 @@
         <v>486</v>
       </c>
       <c r="B487" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C487">
         <v>0</v>
@@ -44304,7 +44311,7 @@
         <v>487</v>
       </c>
       <c r="B488" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C488">
         <v>0</v>
@@ -44390,7 +44397,7 @@
         <v>488</v>
       </c>
       <c r="B489" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C489">
         <v>0</v>
@@ -44476,7 +44483,7 @@
         <v>489</v>
       </c>
       <c r="B490" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C490">
         <v>0</v>
@@ -44562,7 +44569,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C491">
         <v>0</v>
@@ -44734,7 +44741,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C493">
         <v>0</v>
@@ -44820,7 +44827,7 @@
         <v>493</v>
       </c>
       <c r="B494" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C494">
         <v>0</v>
@@ -44906,7 +44913,7 @@
         <v>494</v>
       </c>
       <c r="B495" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C495">
         <v>0</v>
@@ -44992,7 +44999,7 @@
         <v>495</v>
       </c>
       <c r="B496" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C496">
         <v>0</v>
@@ -45078,7 +45085,7 @@
         <v>496</v>
       </c>
       <c r="B497" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C497">
         <v>0</v>
@@ -45336,7 +45343,7 @@
         <v>499</v>
       </c>
       <c r="B500" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C500">
         <v>0</v>
